--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ann\Desktop\Alpha Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{138EF20F-DD8A-4BCD-9D82-14B32431E41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EC2F8B-9FE1-41D3-BEB6-0EBF06CAB553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{3A2B01AA-F2B5-4ED5-801F-A50F83338F2F}"/>
+    <workbookView xWindow="0" yWindow="1290" windowWidth="18135" windowHeight="9630" xr2:uid="{3A2B01AA-F2B5-4ED5-801F-A50F83338F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,16 +27,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>pass</t>
-  </si>
-  <si>
     <t>mgs</t>
   </si>
   <si>
     <t>mgrs</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
   </si>
 </sst>
 </file>
@@ -397,15 +397,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>1234</v>
@@ -413,7 +413,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>2345</v>
